--- a/Data/EC/NIT-9004356287.xlsx
+++ b/Data/EC/NIT-9004356287.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C81B77-E76B-438F-82F5-25BA2AFA9C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F42BF11C-1EBF-46DE-BBF0-F98801878847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D22EC8A5-C5B6-4C4B-84FD-F88603C6CE5A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F2C793A4-2F9F-4477-BE02-3751F973F6A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,169 +71,169 @@
     <t>PATRYS MARGARITA PEÑATA PEREZ</t>
   </si>
   <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -332,9 +332,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -347,7 +345,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -547,23 +547,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -591,10 +591,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -632,22 +632,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC3B11A-F955-8AC1-BAEA-0A385808A0F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{317C5C62-9549-0E98-EB81-9816F278E626}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -669,7 +669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -998,23 +998,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DE4D64-2887-4ECF-A1EC-6EFEF8D4200B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526A1B08-9316-41C7-83A7-E4D8A000A107}">
   <dimension ref="B2:J76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1027,7 +1027,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1038,7 +1038,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1049,7 +1049,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1060,8 +1060,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>67</v>
       </c>
@@ -1076,8 +1076,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1092,8 +1092,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>68</v>
       </c>
@@ -1108,8 +1108,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>69</v>
       </c>
@@ -1128,7 +1128,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>28000</v>
+        <v>24999</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1180,7 +1180,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1203,7 +1203,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1226,7 +1226,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1249,7 +1249,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1272,7 +1272,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1295,7 +1295,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1318,7 +1318,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1341,7 +1341,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1364,7 +1364,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1387,7 +1387,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1410,7 +1410,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1433,7 +1433,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1456,7 +1456,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1479,7 +1479,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1502,7 +1502,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1525,7 +1525,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1548,7 +1548,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1571,7 +1571,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1594,7 +1594,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1617,7 +1617,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1640,7 +1640,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1663,7 +1663,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1686,7 +1686,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1709,7 +1709,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1732,7 +1732,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>28000</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1755,7 +1755,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1778,7 +1778,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1801,7 +1801,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1824,7 +1824,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G45" s="18">
         <v>781242</v>
@@ -1847,7 +1847,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>41</v>
       </c>
       <c r="F46" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G46" s="18">
         <v>781242</v>
@@ -1870,7 +1870,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>42</v>
       </c>
       <c r="F47" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G47" s="18">
         <v>781242</v>
@@ -1893,7 +1893,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>43</v>
       </c>
       <c r="F48" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G48" s="18">
         <v>781242</v>
@@ -1916,7 +1916,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>44</v>
       </c>
       <c r="F49" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G49" s="18">
         <v>781242</v>
@@ -1939,7 +1939,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>45</v>
       </c>
       <c r="F50" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G50" s="18">
         <v>781242</v>
@@ -1962,7 +1962,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G51" s="18">
         <v>781242</v>
@@ -1985,7 +1985,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>47</v>
       </c>
       <c r="F52" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G52" s="18">
         <v>781242</v>
@@ -2008,7 +2008,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>48</v>
       </c>
       <c r="F53" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G53" s="18">
         <v>781242</v>
@@ -2031,7 +2031,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>49</v>
       </c>
       <c r="F54" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G54" s="18">
         <v>781242</v>
@@ -2054,7 +2054,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>50</v>
       </c>
       <c r="F55" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G55" s="18">
         <v>781242</v>
@@ -2077,7 +2077,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>51</v>
       </c>
       <c r="F56" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G56" s="18">
         <v>781242</v>
@@ -2100,7 +2100,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>52</v>
       </c>
       <c r="F57" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G57" s="18">
         <v>781242</v>
@@ -2123,7 +2123,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G58" s="18">
         <v>781242</v>
@@ -2146,7 +2146,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>54</v>
       </c>
       <c r="F59" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G59" s="18">
         <v>781242</v>
@@ -2169,7 +2169,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>55</v>
       </c>
       <c r="F60" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G60" s="18">
         <v>781242</v>
@@ -2192,7 +2192,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>56</v>
       </c>
       <c r="F61" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G61" s="18">
         <v>781242</v>
@@ -2215,7 +2215,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>57</v>
       </c>
       <c r="F62" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G62" s="18">
         <v>781242</v>
@@ -2238,7 +2238,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>58</v>
       </c>
       <c r="F63" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G63" s="18">
         <v>781242</v>
@@ -2261,7 +2261,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>59</v>
       </c>
       <c r="F64" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G64" s="18">
         <v>781242</v>
@@ -2284,7 +2284,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G65" s="18">
         <v>781242</v>
@@ -2307,7 +2307,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>61</v>
       </c>
       <c r="F66" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G66" s="18">
         <v>781242</v>
@@ -2330,7 +2330,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>62</v>
       </c>
       <c r="F67" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G67" s="18">
         <v>781242</v>
@@ -2353,7 +2353,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>63</v>
       </c>
       <c r="F68" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G68" s="18">
         <v>781242</v>
@@ -2376,7 +2376,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>64</v>
       </c>
       <c r="F69" s="18">
-        <v>31249</v>
+        <v>28000</v>
       </c>
       <c r="G69" s="18">
         <v>781242</v>
@@ -2399,7 +2399,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
         <v>8</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>65</v>
       </c>
       <c r="F70" s="24">
-        <v>24999</v>
+        <v>28000</v>
       </c>
       <c r="G70" s="24">
         <v>781242</v>
@@ -2422,7 +2422,7 @@
       <c r="I70" s="25"/>
       <c r="J70" s="26"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="32" t="s">
         <v>75</v>
       </c>
@@ -2433,7 +2433,7 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="32" t="s">
         <v>74</v>
       </c>
